--- a/Delevraibles/PCBWay_BOM.xlsx
+++ b/Delevraibles/PCBWay_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DarkTag-PCBReview\Delevraibles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7260033-E2C8-4B22-AF2F-2846A9B37AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64D14FB-E813-4B0C-B309-B13D00D5AD31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="166">
   <si>
     <t>Component list</t>
   </si>
@@ -428,9 +428,6 @@
     <t>Texas Instruments</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>10uF</t>
   </si>
   <si>
@@ -504,6 +501,33 @@
   </si>
   <si>
     <t>Quantity (1 Board)</t>
+  </si>
+  <si>
+    <t>Item  Type</t>
+  </si>
+  <si>
+    <t>Capacitor</t>
+  </si>
+  <si>
+    <t>Diode</t>
+  </si>
+  <si>
+    <t>Connector</t>
+  </si>
+  <si>
+    <t>Inductor</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>Resistor</t>
+  </si>
+  <si>
+    <t>IC</t>
+  </si>
+  <si>
+    <t>Value</t>
   </si>
 </sst>
 </file>
@@ -677,7 +701,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -896,11 +920,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1054,6 +1115,44 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1082,13 +1181,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>1905000</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -1396,1092 +1495,1159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
-    <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
-      <c r="C1" s="2"/>
+      <c r="C1" s="19"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="56"/>
+      <c r="H1" s="2"/>
       <c r="I1" s="56"/>
       <c r="J1" s="56"/>
-    </row>
-    <row r="2" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="56"/>
+    </row>
+    <row r="2" spans="1:11" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="59"/>
+      <c r="D2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="47" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="3"/>
+      <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="44"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J2" s="3"/>
+      <c r="K2" s="44"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="60"/>
+      <c r="D3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="48" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="4"/>
+      <c r="G3" s="12"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="57"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J3" s="4"/>
+      <c r="K3" s="57"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="60"/>
+      <c r="D4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="49" t="s">
+      <c r="E4" s="12"/>
+      <c r="F4" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="6"/>
+      <c r="G4" s="13"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
-      <c r="J4" s="58"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J4" s="6"/>
+      <c r="K4" s="58"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="60"/>
+      <c r="D5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="12"/>
+      <c r="F5" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="5"/>
+      <c r="G5" s="14"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
-      <c r="J5" s="58"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J5" s="5"/>
+      <c r="K5" s="58"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="61"/>
       <c r="D6" s="15"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="5"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="14"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="58"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J6" s="5"/>
+      <c r="K6" s="58"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
-      <c r="C7" s="17"/>
+      <c r="C7" s="62"/>
       <c r="D7" s="17"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="7"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="17"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="58"/>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J7" s="7"/>
+      <c r="K7" s="58"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
-      <c r="C8" s="27"/>
+      <c r="C8" s="63"/>
       <c r="D8" s="27"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="7"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="17"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
-      <c r="J8" s="58"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J8" s="7"/>
+      <c r="K8" s="58"/>
+    </row>
+    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="D9" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="E9" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="F9" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="F9" s="30" t="s">
+      <c r="G9" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="H9" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="H9" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="I9" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="J9" s="31" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="K9" s="31" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="32">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="E10" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="38" t="s">
+      <c r="F10" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="F10" s="39" t="s">
+      <c r="G10" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="38" t="s">
+      <c r="H10" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="H10" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="I10" s="38">
+      <c r="I10" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="J10" s="38">
         <v>4</v>
       </c>
-      <c r="J10" s="42"/>
-    </row>
-    <row r="11" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K10" s="42"/>
+    </row>
+    <row r="11" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="32">
         <f t="shared" ref="B11:B39" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="67"/>
+      <c r="D11" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="E11" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="40" t="s">
+      <c r="F11" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="F11" s="41" t="s">
+      <c r="G11" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="G11" s="40" t="s">
+      <c r="H11" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="H11" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="I11" s="40">
+      <c r="I11" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="J11" s="40">
         <v>2</v>
       </c>
-      <c r="J11" s="43"/>
-    </row>
-    <row r="12" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K11" s="43"/>
+    </row>
+    <row r="12" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="32">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="67"/>
+      <c r="D12" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="E12" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="F12" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="F12" s="39" t="s">
+      <c r="G12" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="38" t="s">
+      <c r="H12" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="H12" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="I12" s="38">
+      <c r="I12" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="J12" s="38">
         <v>3</v>
       </c>
-      <c r="J12" s="42"/>
-    </row>
-    <row r="13" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K12" s="42"/>
+    </row>
+    <row r="13" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="32">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="67"/>
+      <c r="D13" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="41" t="s">
+      <c r="E13" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="40" t="s">
+      <c r="F13" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="41" t="s">
+      <c r="G13" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="G13" s="40" t="s">
+      <c r="H13" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="H13" s="41" t="s">
-        <v>135</v>
-      </c>
-      <c r="I13" s="40">
+      <c r="I13" s="41" t="s">
+        <v>134</v>
+      </c>
+      <c r="J13" s="40">
         <v>2</v>
       </c>
-      <c r="J13" s="43"/>
-    </row>
-    <row r="14" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K13" s="43"/>
+    </row>
+    <row r="14" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="32">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="67"/>
+      <c r="D14" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="E14" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="38" t="s">
+      <c r="F14" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="F14" s="39" t="s">
+      <c r="G14" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="G14" s="38" t="s">
+      <c r="H14" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="H14" s="39" t="s">
-        <v>136</v>
-      </c>
-      <c r="I14" s="38">
+      <c r="I14" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="J14" s="38">
         <v>2</v>
       </c>
-      <c r="J14" s="42"/>
-    </row>
-    <row r="15" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K14" s="42"/>
+    </row>
+    <row r="15" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="32">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="67"/>
+      <c r="D15" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="41" t="s">
+      <c r="E15" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="40" t="s">
+      <c r="F15" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="F15" s="41" t="s">
+      <c r="G15" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="G15" s="40" t="s">
+      <c r="H15" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="H15" s="41" t="s">
-        <v>137</v>
-      </c>
-      <c r="I15" s="40">
+      <c r="I15" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="J15" s="40">
         <v>2</v>
       </c>
-      <c r="J15" s="43"/>
-    </row>
-    <row r="16" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K15" s="43"/>
+    </row>
+    <row r="16" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="32">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="67"/>
+      <c r="D16" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="E16" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="38" t="s">
+      <c r="F16" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="G16" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="G16" s="38" t="s">
+      <c r="H16" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="H16" s="39" t="s">
-        <v>138</v>
-      </c>
-      <c r="I16" s="38">
+      <c r="I16" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="J16" s="38">
         <v>2</v>
       </c>
-      <c r="J16" s="42"/>
-    </row>
-    <row r="17" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K16" s="42"/>
+    </row>
+    <row r="17" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="32">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="67"/>
+      <c r="D17" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="41" t="s">
+      <c r="E17" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="40" t="s">
+      <c r="F17" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="41" t="s">
+      <c r="G17" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="G17" s="40" t="s">
+      <c r="H17" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="H17" s="41" t="s">
-        <v>139</v>
-      </c>
-      <c r="I17" s="40">
+      <c r="I17" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="J17" s="40">
         <v>1</v>
       </c>
-      <c r="J17" s="43"/>
-    </row>
-    <row r="18" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K17" s="43"/>
+    </row>
+    <row r="18" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="32">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="67"/>
+      <c r="D18" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="E18" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="F18" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="G18" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="G18" s="38" t="s">
+      <c r="H18" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="H18" s="39" t="s">
-        <v>140</v>
-      </c>
-      <c r="I18" s="38">
+      <c r="I18" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="J18" s="38">
         <v>1</v>
       </c>
-      <c r="J18" s="42"/>
-    </row>
-    <row r="19" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K18" s="42"/>
+    </row>
+    <row r="19" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="32">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C19" s="67"/>
+      <c r="D19" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="41" t="s">
+      <c r="E19" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="40" t="s">
+      <c r="F19" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="F19" s="41" t="s">
+      <c r="G19" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="G19" s="40" t="s">
+      <c r="H19" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="H19" s="41" t="s">
-        <v>141</v>
-      </c>
-      <c r="I19" s="40">
+      <c r="I19" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="J19" s="40">
         <v>1</v>
       </c>
-      <c r="J19" s="43"/>
-    </row>
-    <row r="20" spans="1:10" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K19" s="43"/>
+    </row>
+    <row r="20" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="32">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="68"/>
+      <c r="D20" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="39" t="s">
+      <c r="E20" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="E20" s="38" t="s">
+      <c r="F20" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="G20" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="G20" s="38" t="s">
+      <c r="H20" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="H20" s="39" t="s">
-        <v>142</v>
-      </c>
-      <c r="I20" s="38">
+      <c r="I20" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="J20" s="38">
         <v>1</v>
       </c>
-      <c r="J20" s="42"/>
-    </row>
-    <row r="21" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K20" s="42"/>
+    </row>
+    <row r="21" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="32">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="69" t="s">
+        <v>159</v>
+      </c>
+      <c r="D21" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="41" t="s">
+      <c r="E21" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="E21" s="40" t="s">
+      <c r="F21" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="F21" s="41" t="s">
+      <c r="G21" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="G21" s="40" t="s">
+      <c r="H21" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="H21" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="I21" s="40">
+      <c r="I21" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="J21" s="40">
         <v>2</v>
       </c>
-      <c r="J21" s="43"/>
-    </row>
-    <row r="22" spans="1:10" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K21" s="43"/>
+    </row>
+    <row r="22" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="32">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="69" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="39" t="s">
+      <c r="E22" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="53" t="s">
-        <v>156</v>
-      </c>
-      <c r="F22" s="39" t="s">
+      <c r="F22" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="G22" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="G22" s="38" t="s">
+      <c r="H22" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="H22" s="52" t="s">
-        <v>156</v>
-      </c>
-      <c r="I22" s="38">
+      <c r="I22" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="J22" s="38">
         <v>1</v>
       </c>
-      <c r="J22" s="42"/>
-    </row>
-    <row r="23" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K22" s="42"/>
+    </row>
+    <row r="23" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="32">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="40" t="s">
+      <c r="C23" s="66" t="s">
+        <v>161</v>
+      </c>
+      <c r="D23" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="41" t="s">
+      <c r="E23" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="E23" s="54" t="s">
-        <v>156</v>
-      </c>
-      <c r="F23" s="41" t="s">
+      <c r="F23" s="54" t="s">
+        <v>155</v>
+      </c>
+      <c r="G23" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="G23" s="40" t="s">
+      <c r="H23" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="H23" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="I23" s="40">
+      <c r="I23" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="J23" s="40">
         <v>1</v>
       </c>
-      <c r="J23" s="43"/>
-    </row>
-    <row r="24" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K23" s="43"/>
+    </row>
+    <row r="24" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="32">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="C24" s="68"/>
+      <c r="D24" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="39" t="s">
+      <c r="E24" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="E24" s="53" t="s">
-        <v>156</v>
-      </c>
-      <c r="F24" s="39">
+      <c r="F24" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="G24" s="39">
         <v>74404041010</v>
       </c>
-      <c r="G24" s="38" t="s">
+      <c r="H24" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="H24" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="I24" s="38">
+      <c r="I24" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="J24" s="38">
         <v>1</v>
       </c>
-      <c r="J24" s="42"/>
-    </row>
-    <row r="25" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K24" s="42"/>
+    </row>
+    <row r="25" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="32">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="69" t="s">
+        <v>162</v>
+      </c>
+      <c r="D25" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="41" t="s">
+      <c r="E25" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="E25" s="40" t="s">
+      <c r="F25" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="F25" s="41" t="s">
+      <c r="G25" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="G25" s="40" t="s">
+      <c r="H25" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="H25" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="I25" s="40">
+      <c r="I25" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="J25" s="40">
         <v>2</v>
       </c>
-      <c r="J25" s="43"/>
-    </row>
-    <row r="26" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K25" s="43"/>
+    </row>
+    <row r="26" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="32">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="C26" s="66" t="s">
+        <v>160</v>
+      </c>
+      <c r="D26" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="39" t="s">
+      <c r="E26" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="E26" s="38" t="s">
+      <c r="F26" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="F26" s="39">
+      <c r="G26" s="39">
         <v>61300211121</v>
       </c>
-      <c r="G26" s="38" t="s">
+      <c r="H26" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="H26" s="52" t="s">
-        <v>156</v>
-      </c>
-      <c r="I26" s="38">
+      <c r="I26" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="J26" s="38">
         <v>2</v>
       </c>
-      <c r="J26" s="42"/>
-    </row>
-    <row r="27" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K26" s="42"/>
+    </row>
+    <row r="27" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="32">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="40" t="s">
+      <c r="C27" s="67"/>
+      <c r="D27" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="41" t="s">
+      <c r="E27" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="E27" s="40" t="s">
+      <c r="F27" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="F27" s="41" t="s">
+      <c r="G27" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="G27" s="40" t="s">
+      <c r="H27" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="H27" s="55" t="s">
-        <v>156</v>
-      </c>
-      <c r="I27" s="40">
+      <c r="I27" s="55" t="s">
+        <v>155</v>
+      </c>
+      <c r="J27" s="40">
         <v>2</v>
       </c>
-      <c r="J27" s="43"/>
-    </row>
-    <row r="28" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K27" s="43"/>
+    </row>
+    <row r="28" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="32">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="38" t="s">
+      <c r="C28" s="66" t="s">
+        <v>163</v>
+      </c>
+      <c r="D28" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="39" t="s">
+      <c r="E28" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="E28" s="38" t="s">
+      <c r="F28" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="F28" s="39" t="s">
+      <c r="G28" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="G28" s="38" t="s">
+      <c r="H28" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="H28" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="I28" s="38">
+      <c r="I28" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="J28" s="38">
         <v>1</v>
       </c>
-      <c r="J28" s="42"/>
-    </row>
-    <row r="29" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K28" s="42"/>
+    </row>
+    <row r="29" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="32">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="40" t="s">
+      <c r="C29" s="67"/>
+      <c r="D29" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="41" t="s">
+      <c r="E29" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="E29" s="40" t="s">
+      <c r="F29" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="F29" s="41" t="s">
+      <c r="G29" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="G29" s="40" t="s">
+      <c r="H29" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="H29" s="41" t="s">
-        <v>146</v>
-      </c>
-      <c r="I29" s="40">
+      <c r="I29" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="J29" s="40">
         <v>1</v>
       </c>
-      <c r="J29" s="43"/>
-    </row>
-    <row r="30" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K29" s="43"/>
+    </row>
+    <row r="30" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="32">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="38" t="s">
+      <c r="C30" s="67"/>
+      <c r="D30" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="39" t="s">
+      <c r="E30" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="E30" s="38" t="s">
+      <c r="F30" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="F30" s="39" t="s">
+      <c r="G30" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="G30" s="38" t="s">
+      <c r="H30" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="H30" s="39" t="s">
-        <v>147</v>
-      </c>
-      <c r="I30" s="38">
+      <c r="I30" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="J30" s="38">
         <v>7</v>
       </c>
-      <c r="J30" s="42"/>
-    </row>
-    <row r="31" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K30" s="42"/>
+    </row>
+    <row r="31" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="32">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="40" t="s">
+      <c r="C31" s="67"/>
+      <c r="D31" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D31" s="41" t="s">
+      <c r="E31" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="E31" s="40" t="s">
+      <c r="F31" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="F31" s="41" t="s">
+      <c r="G31" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="G31" s="40" t="s">
+      <c r="H31" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="H31" s="41" t="s">
-        <v>148</v>
-      </c>
-      <c r="I31" s="40">
+      <c r="I31" s="41" t="s">
+        <v>147</v>
+      </c>
+      <c r="J31" s="40">
         <v>1</v>
       </c>
-      <c r="J31" s="43"/>
-    </row>
-    <row r="32" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K31" s="43"/>
+    </row>
+    <row r="32" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="32">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="38" t="s">
+      <c r="C32" s="67"/>
+      <c r="D32" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="39" t="s">
+      <c r="E32" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="E32" s="38" t="s">
+      <c r="F32" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="F32" s="39" t="s">
+      <c r="G32" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="G32" s="38" t="s">
+      <c r="H32" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="H32" s="39" t="s">
-        <v>149</v>
-      </c>
-      <c r="I32" s="38">
+      <c r="I32" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="J32" s="38">
         <v>1</v>
       </c>
-      <c r="J32" s="42"/>
-    </row>
-    <row r="33" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K32" s="42"/>
+    </row>
+    <row r="33" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="32">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="40" t="s">
+      <c r="C33" s="67"/>
+      <c r="D33" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="41" t="s">
+      <c r="E33" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="E33" s="40" t="s">
+      <c r="F33" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="F33" s="41" t="s">
+      <c r="G33" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="G33" s="40" t="s">
+      <c r="H33" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="H33" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="I33" s="40">
+      <c r="I33" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="J33" s="40">
         <v>1</v>
       </c>
-      <c r="J33" s="43"/>
-    </row>
-    <row r="34" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K33" s="43"/>
+    </row>
+    <row r="34" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="32">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="38" t="s">
+      <c r="C34" s="67"/>
+      <c r="D34" s="70" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="39" t="s">
+      <c r="E34" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="E34" s="38" t="s">
+      <c r="F34" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="F34" s="39" t="s">
+      <c r="G34" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="G34" s="38" t="s">
+      <c r="H34" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="H34" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="I34" s="38">
+      <c r="I34" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="J34" s="38">
         <v>10</v>
       </c>
-      <c r="J34" s="42"/>
-    </row>
-    <row r="35" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K34" s="42"/>
+    </row>
+    <row r="35" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="32">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="40" t="s">
+      <c r="C35" s="67"/>
+      <c r="D35" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="41" t="s">
+      <c r="E35" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="E35" s="40" t="s">
+      <c r="F35" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="F35" s="41" t="s">
+      <c r="G35" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="G35" s="40" t="s">
+      <c r="H35" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="H35" s="41" t="s">
-        <v>152</v>
-      </c>
-      <c r="I35" s="40">
+      <c r="I35" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="J35" s="40">
         <v>2</v>
       </c>
-      <c r="J35" s="43"/>
-    </row>
-    <row r="36" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K35" s="43"/>
+    </row>
+    <row r="36" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="32">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="38" t="s">
+      <c r="C36" s="67"/>
+      <c r="D36" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="39" t="s">
+      <c r="E36" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="E36" s="38" t="s">
+      <c r="F36" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="F36" s="39" t="s">
+      <c r="G36" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="G36" s="38" t="s">
+      <c r="H36" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="H36" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="I36" s="38">
+      <c r="I36" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="J36" s="38">
         <v>1</v>
       </c>
-      <c r="J36" s="42"/>
-    </row>
-    <row r="37" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K36" s="42"/>
+    </row>
+    <row r="37" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="32">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="40" t="s">
+      <c r="C37" s="68"/>
+      <c r="D37" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="41" t="s">
+      <c r="E37" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E37" s="40" t="s">
+      <c r="F37" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="F37" s="41" t="s">
+      <c r="G37" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="G37" s="40" t="s">
+      <c r="H37" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="H37" s="41" t="s">
-        <v>154</v>
-      </c>
-      <c r="I37" s="40">
+      <c r="I37" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="J37" s="40">
         <v>1</v>
       </c>
-      <c r="J37" s="43"/>
-    </row>
-    <row r="38" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K37" s="43"/>
+    </row>
+    <row r="38" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="32">
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="38" t="s">
+      <c r="C38" s="66" t="s">
+        <v>164</v>
+      </c>
+      <c r="D38" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="D38" s="39" t="s">
+      <c r="E38" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="E38" s="38" t="s">
+      <c r="F38" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="F38" s="39" t="s">
+      <c r="G38" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="G38" s="38" t="s">
+      <c r="H38" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="H38" s="52" t="s">
-        <v>156</v>
-      </c>
-      <c r="I38" s="38">
+      <c r="I38" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="J38" s="38">
         <v>1</v>
       </c>
-      <c r="J38" s="42"/>
-    </row>
-    <row r="39" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K38" s="42"/>
+    </row>
+    <row r="39" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="32">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="40" t="s">
+      <c r="C39" s="67"/>
+      <c r="D39" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="D39" s="41" t="s">
+      <c r="E39" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="E39" s="40" t="s">
+      <c r="F39" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="F39" s="41" t="s">
+      <c r="G39" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="G39" s="40" t="s">
+      <c r="H39" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="H39" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="I39" s="40">
+      <c r="I39" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="J39" s="40">
         <v>1</v>
       </c>
-      <c r="J39" s="43"/>
-    </row>
-    <row r="40" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K39" s="43"/>
+    </row>
+    <row r="40" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="32">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="38" t="s">
+      <c r="C40" s="68"/>
+      <c r="D40" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="D40" s="39" t="s">
+      <c r="E40" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="E40" s="38" t="s">
+      <c r="F40" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="F40" s="39" t="s">
+      <c r="G40" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="G40" s="38" t="s">
+      <c r="H40" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="H40" s="52" t="s">
-        <v>156</v>
-      </c>
-      <c r="I40" s="38">
+      <c r="I40" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="J40" s="38">
         <v>1</v>
       </c>
-      <c r="J40" s="42"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K40" s="42"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="33"/>
-      <c r="C41" s="34" t="s">
+      <c r="C41" s="64"/>
+      <c r="D41" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="D41" s="35"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="37"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="36"/>
       <c r="I41" s="37"/>
-      <c r="J41" s="45"/>
-    </row>
-    <row r="42" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J41" s="37"/>
+      <c r="K41" s="45"/>
+    </row>
+    <row r="42" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="24"/>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="65"/>
+      <c r="D42" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
       <c r="G42" s="9"/>
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
-      <c r="J42" s="46"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="46"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="J3:J8"/>
+  <mergeCells count="7">
+    <mergeCell ref="C28:C37"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="K3:K8"/>
+    <mergeCell ref="C10:C20"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C26:C27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
